--- a/Code/LeetCode.xlsx
+++ b/Code/LeetCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\cloud-repository\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0837BAE1-0448-4015-A012-7D00A0CA691B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161AFE13-F1EC-43CF-857C-9963A315E05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D8" s="6">
         <f>COUNTIFS(Easy题单!$B$5:$B$226,B8,Easy题单!$G$5:$G$226,"已完成")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" s="6">
         <f>COUNTIFS(Easy题单!$B$5:$B$226,B8,Easy题单!$G$5:$G$226,"进行中")</f>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="F8" s="8">
         <f t="shared" ref="F8:F20" si="0">IFERROR(D8/C8,0)</f>
-        <v>0.13636363636363635</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>12</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D20" s="2">
         <f>SUM(D8:D19)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2">
         <f>SUM(E8:E19)</f>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="F20" s="9">
         <f t="shared" si="0"/>
-        <v>1.3513513513513514E-2</v>
+        <v>2.2522522522522521E-2</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -3792,7 +3792,7 @@
         <v>62</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" t="s">
@@ -3819,7 +3819,7 @@
         <v>62</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" t="s">
